--- a/data/trans_orig/P33B_R4-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R4-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21305</t>
+          <t>19936</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>24122</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34518</t>
+          <t>36514</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46257</t>
+          <t>46509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>299408</t>
+          <t>306453</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290138</t>
+          <t>298909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304869</t>
+          <t>312280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>267152</t>
+          <t>291939</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258917</t>
+          <t>284051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273492</t>
+          <t>298286</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>566559</t>
+          <t>598392</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>554820</t>
+          <t>588397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575862</t>
+          <t>607336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>37928</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>25665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>53081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>73067</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59348</t>
+          <t>59749</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86380</t>
+          <t>87521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>109100</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90208</t>
+          <t>94072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129561</t>
+          <t>132421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>480677</t>
+          <t>492719</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467445</t>
+          <t>477566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492939</t>
+          <t>504982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>442935</t>
+          <t>472687</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427942</t>
+          <t>458233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454974</t>
+          <t>486005</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>923612</t>
+          <t>965406</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>903151</t>
+          <t>943980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>942504</t>
+          <t>982329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514322</t>
+          <t>545754</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514322</t>
+          <t>545754</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514322</t>
+          <t>545754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032712</t>
+          <t>1076401</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032712</t>
+          <t>1076401</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032712</t>
+          <t>1076401</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51202</t>
+          <t>53211</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39024</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64182</t>
+          <t>67484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>69552</t>
+          <t>71995</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58545</t>
+          <t>60514</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82030</t>
+          <t>84630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>120754</t>
+          <t>125207</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105326</t>
+          <t>107796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139615</t>
+          <t>144733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>262863</t>
+          <t>260816</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249883</t>
+          <t>246543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>275041</t>
+          <t>272174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>279576</t>
+          <t>284386</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267098</t>
+          <t>271751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>290583</t>
+          <t>295867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>542439</t>
+          <t>545202</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>523578</t>
+          <t>525676</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>557867</t>
+          <t>562613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>314027</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>314027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>314027</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>663193</t>
+          <t>670409</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>663193</t>
+          <t>670409</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>663193</t>
+          <t>670409</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57274</t>
+          <t>64535</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74780</t>
+          <t>86096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>99221</t>
+          <t>108924</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57502</t>
+          <t>93401</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127097</t>
+          <t>127819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>156495</t>
+          <t>173460</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112358</t>
+          <t>150250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186982</t>
+          <t>201753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>255283</t>
+          <t>308610</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237777</t>
+          <t>287049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>270134</t>
+          <t>325634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>376090</t>
+          <t>312622</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348214</t>
+          <t>293727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>417809</t>
+          <t>328145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>631372</t>
+          <t>621231</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>600885</t>
+          <t>592938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>675509</t>
+          <t>644441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475311</t>
+          <t>421546</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475311</t>
+          <t>421546</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475311</t>
+          <t>421546</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787867</t>
+          <t>794691</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787867</t>
+          <t>794691</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787867</t>
+          <t>794691</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24403</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31226</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>41837</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30766</t>
+          <t>33492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47205</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>164436</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158031</t>
+          <t>182376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168999</t>
+          <t>195500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>183871</t>
+          <t>200273</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177048</t>
+          <t>192900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189335</t>
+          <t>205789</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>348307</t>
+          <t>390651</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339811</t>
+          <t>382086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356250</t>
+          <t>398996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>38235</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29358</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>49893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62035</t>
+          <t>64118</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52648</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73408</t>
+          <t>74687</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>100693</t>
+          <t>102354</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87962</t>
+          <t>88998</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115328</t>
+          <t>116256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>230978</t>
+          <t>232472</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219723</t>
+          <t>220814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240278</t>
+          <t>241426</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>195021</t>
+          <t>199632</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183648</t>
+          <t>189063</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>204408</t>
+          <t>209902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>425999</t>
+          <t>432103</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>411364</t>
+          <t>418201</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>438730</t>
+          <t>445459</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,35%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>87535</t>
+          <t>105241</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67858</t>
+          <t>84986</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109303</t>
+          <t>131875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>176016</t>
+          <t>216180</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85703</t>
+          <t>192064</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>240594</t>
+          <t>241143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>263550</t>
+          <t>321422</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177484</t>
+          <t>293267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>316694</t>
+          <t>357028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>535715</t>
+          <t>613364</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>513947</t>
+          <t>586730</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>555392</t>
+          <t>633619</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>673249</t>
+          <t>555877</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>608671</t>
+          <t>530914</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>763562</t>
+          <t>579993</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1208964</t>
+          <t>1169240</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1155820</t>
+          <t>1133634</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1295030</t>
+          <t>1197395</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>144085</t>
+          <t>161019</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67830</t>
+          <t>140862</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>205483</t>
+          <t>183767</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>227859</t>
+          <t>255731</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>209266</t>
+          <t>232436</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248594</t>
+          <t>277481</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>371943</t>
+          <t>416750</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>226997</t>
+          <t>387545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>448424</t>
+          <t>451926</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>784635</t>
+          <t>637053</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>723237</t>
+          <t>614305</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>860890</t>
+          <t>657210</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>487533</t>
+          <t>574878</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>466798</t>
+          <t>553128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>506126</t>
+          <t>598173</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1272169</t>
+          <t>1211931</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1195688</t>
+          <t>1176755</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1417115</t>
+          <t>1241136</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>442807</t>
+          <t>487850</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>340557</t>
+          <t>447367</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>491671</t>
+          <t>536492</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>752955</t>
+          <t>840688</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>619270</t>
+          <t>798390</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>825994</t>
+          <t>882710</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1195762</t>
+          <t>1328538</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1026657</t>
+          <t>1270891</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1294178</t>
+          <t>1389085</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3013995</t>
+          <t>3041864</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2965131</t>
+          <t>2993222</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3116245</t>
+          <t>3082347</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2905426</t>
+          <t>2892294</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2832387</t>
+          <t>2850272</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3039111</t>
+          <t>2934592</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5919422</t>
+          <t>5934158</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5821006</t>
+          <t>5873611</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6088527</t>
+          <t>5991805</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
